--- a/Gerbers/BOM.xlsx
+++ b/Gerbers/BOM.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="BOM_Board1_PCB1_2026-07-01" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="BOM_Board1_PCB1_2026-07-21" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -133,7 +133,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>22kΩ</t>
+    <t>22Ω</t>
   </si>
   <si>
     <t>R1,R2,R3,R4,R5,R6</t>
@@ -142,13 +142,13 @@
     <t>R0603</t>
   </si>
   <si>
-    <t>0603WAF2202T5E</t>
-  </si>
-  <si>
-    <t>UNI-ROYAL(厚声)</t>
-  </si>
-  <si>
-    <t>C31850</t>
+    <t>RC0603FR-0722RL</t>
+  </si>
+  <si>
+    <t>YAGEO(国巨)</t>
+  </si>
+  <si>
+    <t>C107701</t>
   </si>
   <si>
     <t>7</t>
